--- a/Docs/01_Category_Master.xlsx
+++ b/Docs/01_Category_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Categories" sheetId="1" r:id="rId1"/>
@@ -135,9 +135,6 @@
     <t>Household &amp; Cleaning</t>
   </si>
   <si>
-    <t>Categories/</t>
-  </si>
-  <si>
     <t>rice/</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>household/</t>
+  </si>
+  <si>
+    <t>Folder name/Categories</t>
   </si>
 </sst>
 </file>
@@ -550,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -561,7 +561,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -572,7 +572,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -594,7 +594,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -605,7 +605,7 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,7 +616,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -627,7 +627,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -649,7 +649,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -660,7 +660,7 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -671,7 +671,7 @@
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -682,7 +682,7 @@
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -693,7 +693,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -704,7 +704,7 @@
         <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -715,7 +715,7 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -726,7 +726,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -737,7 +737,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -748,7 +748,7 @@
         <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
